--- a/Storage/SampleData/Enum.xlsx
+++ b/Storage/SampleData/Enum.xlsx
@@ -1,26 +1,137 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\Storage\SampleData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B0C4A5-88F2-44A6-8E8B-20EC4C6F43C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-16305" yWindow="16305" windowWidth="16410" windowHeight="9975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Enum" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+  <si>
+    <t>enum_category</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum_value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string(64)</t>
+  </si>
+  <si>
+    <t>string(64)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardCondition</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>EnemyUnitExist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 마리수 이하 (-1 무제한)
+value2: 마리수 이상 (-1 무제한)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardEffectTarget</t>
+  </si>
+  <si>
+    <t>OppentUnit</t>
+  </si>
+  <si>
+    <t>value1: 상대 유닛 n장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardEffectTargetCondition</t>
+  </si>
+  <si>
+    <t>PowerUnderOrEqual</t>
+  </si>
+  <si>
+    <t>value1: 파워 이하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardEffectFunctionType</t>
+  </si>
+  <si>
+    <t>KillUnit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 0-승점 미획득, 1-승점 획득</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,13 +139,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,11 +180,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -66,6 +201,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC780932-CA1A-48F4-A036-BFD57D13E0E9}" name="Enum" displayName="Enum" ref="A2:D14" totalsRowShown="0">
+  <autoFilter ref="A2:D14" xr:uid="{BC780932-CA1A-48F4-A036-BFD57D13E0E9}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{7D624EA5-53C1-45CF-89CD-73313249E030}" name="enum_category"/>
+    <tableColumn id="2" xr3:uid="{C13A8ED2-9687-4374-B368-30AE9D9327DB}" name="enum_value"/>
+    <tableColumn id="3" xr3:uid="{12AD507B-D0AD-40F6-ABA8-ABC6B1B2FDD3}" name="enum_index"/>
+    <tableColumn id="4" xr3:uid="{E332F88F-F28A-4669-8A08-0511854F1313}" name="#desc"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +478,181 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:D14"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="4" width="34.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>